--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Infiltrator_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Infiltrator_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R3802005424ec409d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Ra9aa8d0157634376"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R58b9def5eddf429b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rcacb1bc8ab504e2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R6f7d18c6bb7d4c3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R2f830645cff64c4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rc3362c26899147b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R0d96eca4baab42db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R7b0e3e645a234183"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R1eff4260087d40e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R37a1e76587e341d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rc4441356186c4860"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rc41eb537bf6046f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2e17073c07864c7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rb65cff2730994393"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R277ef0b8602d4eb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R0f9b07b57c9a4bc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R3162fb155d9b409a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Ref390338a1b942a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Ra8c31c20026e4221"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R6055cc37e40544c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Re50dd20b61fa4b19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R805a311e16384298"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rbe0c83b52faf478e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Red6cf17a93f64d2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R02b94e1cf8f64bcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rc9c93ce6fc08468c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rc5ac0feacb3244e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R2df3329a48fb41e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rbd65110c60b04d06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rab0cfdfd25d345a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R9547bb35746d44e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rab5a56bb9ee84563"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R15cbc64923664d98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R3ba738d6a1f14321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R080a2a91073f4563"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R1a2b1997f7764b77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R53f4d69235f4489a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R6bf6603bae004d1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Re3bcd6f306934304"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R80be1519d77740a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R320423c843a8415a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R66cfe7c106ea4834"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R43bc9be0fcfc4203"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R18b0b41fc23846b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R7a60d358414f4a7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R0df0633580b7483c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R3e4f0101e2464844"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R757b639868154123"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R46fdc0065b2646da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R4f7069d9dc924fd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R6b2c0386eceb4d89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rcf835e61f4f4468f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rd9a8741cf4554147"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R44c0d48b5b8a4213"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R2ff080fc3b274f8d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2285,11 +2285,11 @@
       </x:c>
       <x:c r="C10" s="39" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Défini")</x:f>
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D10" s="39" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Prototype")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E10" s="39" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Intégré")</x:f>
@@ -3678,11 +3678,11 @@
       </x:c>
       <x:c r="C37" s="41" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D37" s="41" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E37" s="41" t="n">
         <x:f>SUM(E10:E35)</x:f>
@@ -4373,7 +4373,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdabd0f2f1d8f42f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb9ac50096924085"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5096,7 +5096,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdae17b547de04132"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ddc09657b754e09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5465,7 +5465,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6dfdd537c8dc4b36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc306df482f874c7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5787,7 +5787,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b9b886121844a06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf78c199dec9a4122"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6103,7 +6103,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf5ed6dbaf864701"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c1df076caf54380"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6419,7 +6419,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24de884b4a2a4367"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e9a20ea9ecc46c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6841,7 +6841,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01163abde9134091"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6844b3b7d29f40ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7165,7 +7165,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6eeb86783aa24e72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9ea4d57e3504568"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7905,7 +7905,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R402444af828640f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55e1a7c143f34349"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8288,7 +8288,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0745b5dd8ac44573"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd68609572f7a4202"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8315,7 +8315,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="69" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="247" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -8486,7 +8486,7 @@
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="44" customHeight="1">
+    <x:row r="7" ht="68" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>INF-CHR-RANDALL</x:v>
       </x:c>
@@ -8494,7 +8494,7 @@
         <x:v>Randall Ezno</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -8516,7 +8516,9 @@
       </x:c>
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
-      <x:c r="L7" s="9" t="str"/>
+      <x:c r="L7" s="9" t="str">
+        <x:v>Prototype Chroniques : src/universe-actors.js, src/chronicles.js. Identifiant runtime INF-CHR-RANDALL ; contexte d’œuvre/segment et sélection de scène obligatoires.</x:v>
+      </x:c>
       <x:c r="M7" s="9" t="str"/>
       <x:c r="N7" s="9" t="str">
         <x:v>La fiche distingue identité de référence et rôle proposé.</x:v>
@@ -8532,7 +8534,7 @@
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
       <x:c r="S7" s="20" t="str">
-        <x:v>Costume exact à contrôler sur les images originales avant validation 1:1.</x:v>
+        <x:v>Costume exact à contrôler sur les images originales avant validation 1:1. Prototype partiel disponible dans les Chroniques indépendantes : profil ATB sans portrait, sprite ou moveset complet ; pouvoirs non implémentés signalés. Aucun transfert vers ME1 ni validation 1:1.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
@@ -8616,7 +8618,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75b7b75336d242ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ca1735513a44bf4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9189,7 +9191,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35de8bcecd584317"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf53f699fd8494043"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9505,7 +9507,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6716d971fd740f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67fc1f34bae349df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10371,7 +10373,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0881311bb6b247b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf9361c217f04ef8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10687,7 +10689,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d2bd695238640e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39d87bcab2c74a36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11001,7 +11003,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8562a244fcb84154"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c60ed85c4a34b92"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11446,7 +11448,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4531e747e08d48d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R836cd8666bfe4246"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11881,7 +11883,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47527bc635a5409c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R414a64a86c0f4e49"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12193,7 +12195,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c325c59f1144a9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4946edfaa74f44e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12305,12 +12307,12 @@
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
     </x:row>
-    <x:row r="10" ht="40" customHeight="1">
+    <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Un parcours d’infiltration et de fuite réinterprété en ATB avec sprites 2D et environnements 3D.</x:v>
+        <x:v>Un parcours d’infiltration et de fuite réinterprété en ATB avec sprites 2D et environnements 3D. Prototype partiel : 1 profils sélectionnables et 0 équipements en Chroniques ; le reste demeure documentaire.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -12329,7 +12331,7 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
@@ -12719,10 +12721,16 @@
       <x:c r="E40" s="2"/>
       <x:c r="F40" s="2"/>
     </x:row>
-    <x:row r="41" ht="22" customHeight="1">
-      <x:c r="A41" s="2"/>
-      <x:c r="B41" s="2"/>
-      <x:c r="C41" s="2"/>
+    <x:row r="41" ht="96" customHeight="1">
+      <x:c r="A41" s="6" t="str">
+        <x:v>Prototype Chroniques indépendant</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="str">
+        <x:v>1 personnages sélectionnables, 0 équipements utilisables sous restrictions d’œuvre, segment, scène et porteur ; preuves dans implementationPaths et evidence des seules lignes Prototype.</x:v>
+      </x:c>
+      <x:c r="C41" s="6" t="str">
+        <x:v>Campagne complète, dialogues, acquisition canonique, sprites, costumes, animations et statistiques originales à réaliser ou vérifier. Les ateliers sont des essais de préparation ATB, sans progression canonique ni transfert ME1.</x:v>
+      </x:c>
       <x:c r="D41" s="2"/>
       <x:c r="E41" s="2"/>
       <x:c r="F41" s="2"/>
@@ -13278,6 +13286,14 @@
       <x:c r="D110" s="2"/>
       <x:c r="E110" s="2"/>
       <x:c r="F110" s="2"/>
+    </x:row>
+    <x:row r="111" ht="22" customHeight="1">
+      <x:c r="A111" s="2"/>
+      <x:c r="B111" s="2"/>
+      <x:c r="C111" s="2"/>
+      <x:c r="D111" s="2"/>
+      <x:c r="E111" s="2"/>
+      <x:c r="F111" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13646,7 +13662,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra25783737ced47ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb745ef2eb7194330"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13970,7 +13986,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b3a611391864b3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R086244832880462c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14341,7 +14357,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R323522df387f4d32"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18007ac11b3342ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15089,7 +15105,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re87b79640f784af2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R118f8fd5312f4794"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15405,7 +15421,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6f597f887b747c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37ffd769120a4da2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15788,7 +15804,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0a897514a254d72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50083888d6954afd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16147,7 +16163,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8867ea199f04fbf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe76e00fa96f441e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Infiltrator_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Infiltrator_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R2df3329a48fb41e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rbd65110c60b04d06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rab0cfdfd25d345a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R9547bb35746d44e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rab5a56bb9ee84563"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R15cbc64923664d98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R3ba738d6a1f14321"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R080a2a91073f4563"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R1a2b1997f7764b77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R53f4d69235f4489a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R6bf6603bae004d1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Re3bcd6f306934304"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R80be1519d77740a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R320423c843a8415a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R66cfe7c106ea4834"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R43bc9be0fcfc4203"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R18b0b41fc23846b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R7a60d358414f4a7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R0df0633580b7483c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R3e4f0101e2464844"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R757b639868154123"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R46fdc0065b2646da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R4f7069d9dc924fd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R6b2c0386eceb4d89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rcf835e61f4f4468f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rd9a8741cf4554147"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R44c0d48b5b8a4213"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R2ff080fc3b274f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R349c0a6dda904283"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rd8a31b9ef7514046"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R9de5698db5be473b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rb50ab76250f84be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R45a6fcebadb1435c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R9aebcdc7a9b447d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Raa67c91d80f84d3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Ra388328fcae641c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R5ebb4612409b426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rd1d30c37b3b646bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R8418b1a2c4fc4687"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Re68858c53a7248c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Ra838ab0e38e94860"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R56f63c0980d34c7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R45124b6355864acd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R97a75160e67545fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R8c7811ec08c54dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rd187a9b9c7814fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R1f52f9020d294f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R235ed135c32248e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R6611d0d501ba48b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R65b271eba26044e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R84c31b32e24843eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R1994ee592f1b4089"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rb3e01d5fcadc42fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R0fad0919b87e4fa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rc782ee46a1694ad6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rc17fa0f83e6b43d6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>109</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>10</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>62</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Défini")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Prototype")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="39" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D12" s="39" t="n">
+      <x:c r="D12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E12" s="39" t="n">
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D13" s="40" t="n">
+      <x:c r="D13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="40" t="n">
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$13,"Établi")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$13,"P0")</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$15)</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$15,"Défini")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$15,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$15,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$15,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$15,"Établi")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$15,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$15,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$15,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$15,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$15,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$15,"P0")</x:f>
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$10,"Établi")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$13,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$18)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$18,"Défini")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$18,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$18,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$18,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$18,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$18,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$18,"Extrapolation")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$18,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$18,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$18,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$18,"P0")</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$11,"P0")</x:f>
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$11,"P0")</x:f>
         <x:v>5</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="n">
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="40" t="n">
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>109</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D37" s="41" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E37" s="41" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>62</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>21</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4040,10 +4034,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>PV, dégâts, cadence et nombre d’unités à équilibrer pour le fan game.</x:v>
       </x:c>
     </x:row>
@@ -4089,10 +4083,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>PV, dégâts, cadence et nombre d’unités à équilibrer pour le fan game.</x:v>
       </x:c>
     </x:row>
@@ -4138,10 +4132,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>PV, dégâts, cadence et nombre d’unités à équilibrer pour le fan game.</x:v>
       </x:c>
     </x:row>
@@ -4187,10 +4181,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>PV, dégâts, cadence et nombre d’unités à équilibrer pour le fan game.</x:v>
       </x:c>
     </x:row>
@@ -4236,10 +4230,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>PV, dégâts, cadence et nombre d’unités à équilibrer pour le fan game.</x:v>
       </x:c>
     </x:row>
@@ -4285,10 +4279,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>PV, dégâts, cadence et nombre d’unités à équilibrer pour le fan game.</x:v>
       </x:c>
     </x:row>
@@ -4334,10 +4328,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>PV, dégâts, cadence et nombre d’unités à équilibrer pour le fan game.</x:v>
       </x:c>
     </x:row>
@@ -4373,7 +4367,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb9ac50096924085"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb80613be6e8140c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4513,61 +4507,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4617,10 +4611,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INF-GUIDE</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator_Guide</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le nom et la place du chapitre sont référencés. Son agencement ATB est original.</x:v>
       </x:c>
     </x:row>
@@ -4672,10 +4666,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INF-GUIDE</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator_Guide</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le nom et la place du chapitre sont référencés. Son agencement ATB est original.</x:v>
       </x:c>
     </x:row>
@@ -4727,10 +4721,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>INF-GUIDE</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator_Guide</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le nom et la place du chapitre sont référencés. Son agencement ATB est original.</x:v>
       </x:c>
     </x:row>
@@ -4782,10 +4776,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>INF-GUIDE</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator_Guide</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le nom et la place du chapitre sont référencés. Son agencement ATB est original.</x:v>
       </x:c>
     </x:row>
@@ -4837,10 +4831,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>INF-GUIDE</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator_Guide</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Le nom et la place du chapitre sont référencés. Son agencement ATB est original.</x:v>
       </x:c>
     </x:row>
@@ -4892,10 +4886,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>INF-GUIDE</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator_Guide</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Le nom et la place du chapitre sont référencés. Son agencement ATB est original.</x:v>
       </x:c>
     </x:row>
@@ -4947,10 +4941,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>INF-GUIDE</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator_Guide</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Le nom et la place du chapitre sont référencés. Son agencement ATB est original.</x:v>
       </x:c>
     </x:row>
@@ -5002,10 +4996,10 @@
       <x:c r="Q14" s="7" t="str">
         <x:v>INF-GUIDE</x:v>
       </x:c>
-      <x:c r="R14" s="21" t="str">
+      <x:c r="R14" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator_Guide</x:v>
       </x:c>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="S14" s="7" t="str">
         <x:v>Le nom et la place du chapitre sont référencés. Son agencement ATB est original.</x:v>
       </x:c>
     </x:row>
@@ -5057,10 +5051,10 @@
       <x:c r="Q15" s="9" t="str">
         <x:v>INF-GUIDE</x:v>
       </x:c>
-      <x:c r="R15" s="20" t="str">
+      <x:c r="R15" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator_Guide</x:v>
       </x:c>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="S15" s="9" t="str">
         <x:v>Le nom et la place du chapitre sont référencés. Son agencement ATB est original.</x:v>
       </x:c>
     </x:row>
@@ -5096,7 +5090,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ddc09657b754e09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re65fb5f2610f4253"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5236,61 +5230,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5336,10 +5330,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INF-GUIDE</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator_Guide</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5383,10 +5377,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INF-OFFICIAL</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://koolhausgames.com/portfolio/mass-effect-3/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5428,10 +5422,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>INF-GUIDE</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator_Guide</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -5465,7 +5459,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc306df482f874c7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76a8b1d65a704b0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5605,61 +5599,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5703,10 +5697,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5750,10 +5744,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -5787,7 +5781,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf78c199dec9a4122"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec01aff071554427"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5927,61 +5921,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6025,8 +6019,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -6068,8 +6062,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -6103,7 +6097,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c1df076caf54380"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96e92acd50124a9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6243,61 +6237,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6341,8 +6335,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -6384,8 +6378,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -6419,7 +6413,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e9a20ea9ecc46c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1181b2cc2714120"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6559,65 +6553,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="44" customHeight="1">
+    <x:row r="7" ht="68" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>INF-WPN-MATTOCK</x:v>
       </x:c>
@@ -6659,13 +6653,13 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INF-EQUIP, INF-STORE</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Equipment_(Mass_Effect:_Infiltrator)
 https://masseffect.fandom.com/wiki/Store_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
-    </x:row>
-    <x:row r="8" ht="44" customHeight="1">
+      <x:c r="S7" s="9" t="str"/>
+    </x:row>
+    <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
         <x:v>INF-WPN-EVISCERATOR</x:v>
       </x:c>
@@ -6707,13 +6701,13 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INF-EQUIP, INF-STORE</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Equipment_(Mass_Effect:_Infiltrator)
 https://masseffect.fandom.com/wiki/Store_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str"/>
-    </x:row>
-    <x:row r="9" ht="44" customHeight="1">
+      <x:c r="S8" s="7" t="str"/>
+    </x:row>
+    <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
         <x:v>INF-WPN-INCISOR</x:v>
       </x:c>
@@ -6755,13 +6749,13 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>INF-EQUIP, INF-STORE</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Equipment_(Mass_Effect:_Infiltrator)
 https://masseffect.fandom.com/wiki/Store_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str"/>
-    </x:row>
-    <x:row r="10" ht="44" customHeight="1">
+      <x:c r="S9" s="9" t="str"/>
+    </x:row>
+    <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
         <x:v>INF-WPN-PARTICLE</x:v>
       </x:c>
@@ -6803,11 +6797,11 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>INF-EQUIP, INF-STORE</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Equipment_(Mass_Effect:_Infiltrator)
 https://masseffect.fandom.com/wiki/Store_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -6841,7 +6835,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6844b3b7d29f40ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb73890005c3243b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6981,61 +6975,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7081,10 +7075,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INF-EQUIP</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Equipment_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7128,10 +7122,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INF-OFFICIAL</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://koolhausgames.com/portfolio/mass-effect-3/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -7165,7 +7159,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9ea4d57e3504568"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8007dea9880c4c07"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7305,61 +7299,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7407,10 +7401,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INF-STORE</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Store_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Source secondaire partielle. Les règles ATB proposées ne constituent pas une validation de la capacité originale.</x:v>
       </x:c>
     </x:row>
@@ -7458,10 +7452,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INF-STORE</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Store_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Source secondaire partielle. Les règles ATB proposées ne constituent pas une validation de la capacité originale.</x:v>
       </x:c>
     </x:row>
@@ -7509,10 +7503,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>INF-STORE</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Store_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Source secondaire partielle. Les règles ATB proposées ne constituent pas une validation de la capacité originale.</x:v>
       </x:c>
     </x:row>
@@ -7560,10 +7554,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>INF-STORE</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Store_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Source secondaire partielle. Les règles ATB proposées ne constituent pas une validation de la capacité originale.</x:v>
       </x:c>
     </x:row>
@@ -7611,10 +7605,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>INF-STORE</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Store_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Source secondaire partielle. Les règles ATB proposées ne constituent pas une validation de la capacité originale.</x:v>
       </x:c>
     </x:row>
@@ -7662,10 +7656,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>INF-STORE</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Store_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Source secondaire partielle. Les règles ATB proposées ne constituent pas une validation de la capacité originale.</x:v>
       </x:c>
     </x:row>
@@ -7713,10 +7707,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>INF-STORE</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Store_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Source secondaire partielle. Les règles ATB proposées ne constituent pas une validation de la capacité originale.</x:v>
       </x:c>
     </x:row>
@@ -7764,10 +7758,10 @@
       <x:c r="Q14" s="7" t="str">
         <x:v>INF-STORE</x:v>
       </x:c>
-      <x:c r="R14" s="21" t="str">
+      <x:c r="R14" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Store_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="S14" s="7" t="str">
         <x:v>Source secondaire partielle. Les règles ATB proposées ne constituent pas une validation de la capacité originale.</x:v>
       </x:c>
     </x:row>
@@ -7815,10 +7809,10 @@
       <x:c r="Q15" s="9" t="str">
         <x:v>INF-STORE</x:v>
       </x:c>
-      <x:c r="R15" s="20" t="str">
+      <x:c r="R15" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Store_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="S15" s="9" t="str">
         <x:v>Source secondaire partielle. Les règles ATB proposées ne constituent pas une validation de la capacité originale.</x:v>
       </x:c>
     </x:row>
@@ -7866,10 +7860,10 @@
       <x:c r="Q16" s="7" t="str">
         <x:v>INF-STORE</x:v>
       </x:c>
-      <x:c r="R16" s="21" t="str">
+      <x:c r="R16" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Store_(Mass_Effect:_Infiltrator)</x:v>
       </x:c>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="S16" s="7" t="str">
         <x:v>Source secondaire partielle. Les règles ATB proposées ne constituent pas une validation de la capacité originale.</x:v>
       </x:c>
     </x:row>
@@ -7905,7 +7899,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55e1a7c143f34349"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ecc30975a00414c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8045,61 +8039,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8151,8 +8145,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8202,8 +8196,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8253,8 +8247,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -8288,7 +8282,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd68609572f7a4202"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67bc7fc48a1e4edd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8315,7 +8309,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="69" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="247" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -8428,61 +8422,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8530,14 +8524,14 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Costume exact à contrôler sur les images originales avant validation 1:1. Prototype partiel disponible dans les Chroniques indépendantes : profil ATB sans portrait, sprite ou moveset complet ; pouvoirs non implémentés signalés. Aucun transfert vers ME1 ni validation 1:1.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="44" customHeight="1">
+    <x:row r="8" ht="124" customHeight="1">
       <x:c r="A8" s="19" t="str">
         <x:v>INF-CHR-TURIAN</x:v>
       </x:c>
@@ -8545,7 +8539,7 @@
         <x:v>Prisonnier turien</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
         <x:v>Établi</x:v>
@@ -8567,7 +8561,9 @@
       </x:c>
       <x:c r="J8" s="7" t="str"/>
       <x:c r="K8" s="7" t="str"/>
-      <x:c r="L8" s="7" t="str"/>
+      <x:c r="L8" s="7" t="str">
+        <x:v>Prototype de profil sélectionnable dans inf-incarceration via src/universe-specialist-scenarios.js et src/universe-actors.js. Conditions de contenu, présence et survie affichées ; mannequins originaux et dotation abstraite, sans mission ni recrutement de campagne. Aucun portrait, sprite ou costume de ce personnage produit.</x:v>
+      </x:c>
       <x:c r="M8" s="7" t="str"/>
       <x:c r="N8" s="7" t="str">
         <x:v>La fiche distingue identité de référence et rôle proposé.</x:v>
@@ -8579,11 +8575,11 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
-        <x:v>Costume exact à contrôler sur les images originales avant validation 1:1.</x:v>
+      <x:c r="S8" s="7" t="str">
+        <x:v>Costume exact à contrôler sur les images originales avant validation 1:1. Profil partiel à statistiques ATB, limité aux bancs déclarés et à leur état préparé. Les conditions de contenu et de disponibilité affichées par le banc sont des prérequis de son état préparé, pas des choix de campagne accordés.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8618,7 +8614,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ca1735513a44bf4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bf27920e86f472c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8758,61 +8754,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8862,8 +8858,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8911,8 +8907,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8960,8 +8956,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9009,8 +9005,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -9058,8 +9054,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -9107,8 +9103,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="44" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -9156,8 +9152,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D13">
@@ -9191,7 +9187,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf53f699fd8494043"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R079eaf8b931d4fb0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9331,61 +9327,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9429,8 +9425,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9472,8 +9468,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -9507,7 +9503,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67fc1f34bae349df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R675001df70004548"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9647,61 +9643,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9753,8 +9749,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Le nombre de poses est une cible de production, pas une donnée du jeu source.</x:v>
       </x:c>
     </x:row>
@@ -9806,8 +9802,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Le nombre de poses est une cible de production, pas une donnée du jeu source.</x:v>
       </x:c>
     </x:row>
@@ -9859,8 +9855,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -9912,8 +9908,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -9965,8 +9961,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -10018,8 +10014,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -10071,8 +10067,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -10124,8 +10120,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -10177,8 +10173,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -10230,8 +10226,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -10283,8 +10279,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str">
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -10336,8 +10332,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str">
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -10373,7 +10369,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf9361c217f04ef8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafe10a03f5c34a79"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10513,61 +10509,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10611,8 +10607,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10654,8 +10650,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -10689,7 +10685,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39d87bcab2c74a36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ccc555dd5424537"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10829,61 +10825,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10927,8 +10923,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10968,8 +10964,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -11003,7 +10999,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c60ed85c4a34b92"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf79efca4be6c43e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11143,61 +11139,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11241,8 +11237,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11284,8 +11280,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11327,8 +11323,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11370,8 +11366,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -11413,8 +11409,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -11448,7 +11444,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R836cd8666bfe4246"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R550bc47e84794ab8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11588,61 +11584,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11684,8 +11680,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11725,8 +11721,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11766,8 +11762,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11807,8 +11803,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -11848,8 +11844,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -11883,7 +11879,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R414a64a86c0f4e49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf6e31c3a87a42a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12023,61 +12019,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12119,8 +12115,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12160,8 +12156,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -12195,7 +12191,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4946edfaa74f44e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ae023090a334370"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12260,10 +12256,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -12307,12 +12303,12 @@
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
     </x:row>
-    <x:row r="10" ht="68" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Un parcours d’infiltration et de fuite réinterprété en ATB avec sprites 2D et environnements 3D. Prototype partiel : 1 profils sélectionnables et 0 équipements en Chroniques ; le reste demeure documentaire.</x:v>
+        <x:v>109 fiches de production ; 2 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -12335,7 +12331,7 @@
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -12488,22 +12484,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -12652,13 +12648,13 @@
       <x:c r="F35" s="2"/>
     </x:row>
     <x:row r="36" ht="34" customHeight="1">
-      <x:c r="A36" s="30" t="str">
+      <x:c r="A36" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B36" s="31" t="str">
+      <x:c r="B36" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C36" s="32" t="str">
+      <x:c r="C36" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D36" s="2"/>
@@ -12726,7 +12722,7 @@
         <x:v>Prototype Chroniques indépendant</x:v>
       </x:c>
       <x:c r="B41" s="6" t="str">
-        <x:v>1 personnages sélectionnables, 0 équipements utilisables sous restrictions d’œuvre, segment, scène et porteur ; preuves dans implementationPaths et evidence des seules lignes Prototype.</x:v>
+        <x:v>2 personnages sélectionnables, 0 équipements utilisables sous restrictions d’œuvre, segment, scène et porteur ; preuves dans implementationPaths et evidence des seules lignes Prototype.</x:v>
       </x:c>
       <x:c r="C41" s="6" t="str">
         <x:v>Campagne complète, dialogues, acquisition canonique, sprites, costumes, animations et statistiques originales à réaliser ou vérifier. Les ateliers sont des essais de préparation ATB, sans progression canonique ni transfert ME1.</x:v>
@@ -12735,10 +12731,16 @@
       <x:c r="E41" s="2"/>
       <x:c r="F41" s="2"/>
     </x:row>
-    <x:row r="42" ht="22" customHeight="1">
-      <x:c r="A42" s="2"/>
-      <x:c r="B42" s="2"/>
-      <x:c r="C42" s="2"/>
+    <x:row r="42" ht="110" customHeight="1">
+      <x:c r="A42" s="6" t="str">
+        <x:v>Complément spécialistes contextualisés</x:v>
+      </x:c>
+      <x:c r="B42" s="6" t="str">
+        <x:v>1 profils supplémentaires limités aux bancs de spécialistes, 0 profils d’armes spéciales et 0 fiches de pouvoirs supplémentaires effectivement exposées. Vérification fonctionnelle liée au rapport docs/qa/chronicle-specialists-browser-report.json.</x:v>
+      </x:c>
+      <x:c r="C42" s="6" t="str">
+        <x:v>Bancs ATB sur mannequins originaux, conditions préparées et dotations abstraites ; aucune reconstruction des missions, acquisition de campagne, illustration, animation, doublage ni valeur originale certifiée. Les sources secondaires et incertitudes restent explicites.</x:v>
+      </x:c>
       <x:c r="D42" s="2"/>
       <x:c r="E42" s="2"/>
       <x:c r="F42" s="2"/>
@@ -13294,6 +13296,14 @@
       <x:c r="D111" s="2"/>
       <x:c r="E111" s="2"/>
       <x:c r="F111" s="2"/>
+    </x:row>
+    <x:row r="112" ht="22" customHeight="1">
+      <x:c r="A112" s="2"/>
+      <x:c r="B112" s="2"/>
+      <x:c r="C112" s="2"/>
+      <x:c r="D112" s="2"/>
+      <x:c r="E112" s="2"/>
+      <x:c r="F112" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13435,61 +13445,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13533,10 +13543,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13580,10 +13590,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13625,10 +13635,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -13662,7 +13672,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb745ef2eb7194330"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe7dc6d291b94477"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13802,61 +13812,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13902,10 +13912,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INF-OFFICIAL</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://koolhausgames.com/portfolio/mass-effect-3/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13949,10 +13959,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -13986,7 +13996,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R086244832880462c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1063edf2b8614cda"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14126,61 +14136,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -14226,10 +14236,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -14273,10 +14283,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -14320,10 +14330,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>INF-WIKI</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Infiltrator</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -14357,7 +14367,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18007ac11b3342ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec90d7d073364dfc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14497,61 +14507,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -14601,8 +14611,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -14650,8 +14660,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -14699,8 +14709,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -14752,8 +14762,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -14805,8 +14815,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -14858,8 +14868,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -14911,8 +14921,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -14964,8 +14974,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -15017,8 +15027,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -15070,8 +15080,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -15105,7 +15115,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R118f8fd5312f4794"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R388bfed04fdc4f27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15245,61 +15255,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15343,8 +15353,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -15386,8 +15396,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -15421,7 +15431,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37ffd769120a4da2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2a56818e5af48f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15561,61 +15571,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15667,8 +15677,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -15718,8 +15728,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -15769,8 +15779,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -15804,7 +15814,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50083888d6954afd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb42a0c655ad14ed7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15944,61 +15954,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16042,8 +16052,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -16085,8 +16095,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -16128,8 +16138,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -16163,7 +16173,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe76e00fa96f441e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd757cb3956244416"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Infiltrator_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Infiltrator_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R349c0a6dda904283"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rd8a31b9ef7514046"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R9de5698db5be473b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rb50ab76250f84be1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R45a6fcebadb1435c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R9aebcdc7a9b447d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Raa67c91d80f84d3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Ra388328fcae641c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R5ebb4612409b426b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rd1d30c37b3b646bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R8418b1a2c4fc4687"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Re68858c53a7248c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Ra838ab0e38e94860"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R56f63c0980d34c7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R45124b6355864acd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R97a75160e67545fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R8c7811ec08c54dff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rd187a9b9c7814fca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R1f52f9020d294f80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R235ed135c32248e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R6611d0d501ba48b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R65b271eba26044e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R84c31b32e24843eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R1994ee592f1b4089"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rb3e01d5fcadc42fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R0fad0919b87e4fa5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rc782ee46a1694ad6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rc17fa0f83e6b43d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Raebd1f102163441d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rc9d2768d69374e48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R62b70856a7c74225"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rd235e793aaa642b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Racabbe7b1369421d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rfb922114eb73434a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R2878a92cd9824dcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R6e454b32082848c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R92204f9628e04a80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Refe353d167014154"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R96b0be3cb3e84ded"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R01622c04699d4899"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rd1867bc4eaa74203"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rb8b8549bc8b94c35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R2c0cd7f450d14da0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R306aae74a10f49f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R7d3cd7e78c794d56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R7f73392355db4481"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rc5ba8c168e534204"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rbc9b4d7dbc5f492a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R5c51d63aa2e04318"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R111d2ca6c0964943"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rb6d0b2fb3af44f84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Ra25fc7bc48ef469f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rd2454d38fe9e47bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Ra6899c543f454946"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R1cf4369c0cff4e12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R3c77084ea0504b36"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4367,7 +4367,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb80613be6e8140c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recb18b5570394865"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5090,7 +5090,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re65fb5f2610f4253"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94c28d59861c41d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5459,7 +5459,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76a8b1d65a704b0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f4ec0bd4dc04e64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5781,7 +5781,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec01aff071554427"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raad78bc467e44bca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6097,7 +6097,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96e92acd50124a9f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1837d2b1ea524e9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6413,7 +6413,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1181b2cc2714120"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R999bfac5c478450e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6835,7 +6835,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb73890005c3243b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc24ecb30885b48c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7159,7 +7159,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8007dea9880c4c07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d759df862204570"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7899,7 +7899,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ecc30975a00414c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fcbd82954844c81"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8282,7 +8282,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67bc7fc48a1e4edd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5fc9e0628064f3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8614,7 +8614,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bf27920e86f472c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bb16815d2734431"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9187,7 +9187,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R079eaf8b931d4fb0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d7f00158f3440c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9503,7 +9503,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R675001df70004548"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R308d60f745e241d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10369,7 +10369,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafe10a03f5c34a79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a179570760f43f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10685,7 +10685,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ccc555dd5424537"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c8d56e0c107434f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10999,7 +10999,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf79efca4be6c43e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4597be362bd4cc9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11444,7 +11444,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R550bc47e84794ab8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra059169d33e04460"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11879,7 +11879,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf6e31c3a87a42a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf461c0a8b9ad438e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12191,7 +12191,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ae023090a334370"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59c775af8cf5462f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13672,7 +13672,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe7dc6d291b94477"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb02885a62e0f4f8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13996,7 +13996,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1063edf2b8614cda"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6075db1c7c3646f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14367,7 +14367,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec90d7d073364dfc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36ca155bacc147f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15115,7 +15115,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R388bfed04fdc4f27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3cd3d7cb8714326"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15431,7 +15431,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2a56818e5af48f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02d3736283fc47d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15814,7 +15814,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb42a0c655ad14ed7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree75f5a7ceaa436d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16173,7 +16173,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd757cb3956244416"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra24e92cea1604394"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Infiltrator_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Infiltrator_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Raebd1f102163441d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rc9d2768d69374e48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R62b70856a7c74225"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rd235e793aaa642b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Racabbe7b1369421d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rfb922114eb73434a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R2878a92cd9824dcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R6e454b32082848c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R92204f9628e04a80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Refe353d167014154"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R96b0be3cb3e84ded"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R01622c04699d4899"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rd1867bc4eaa74203"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rb8b8549bc8b94c35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R2c0cd7f450d14da0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R306aae74a10f49f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R7d3cd7e78c794d56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R7f73392355db4481"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rc5ba8c168e534204"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rbc9b4d7dbc5f492a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R5c51d63aa2e04318"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R111d2ca6c0964943"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rb6d0b2fb3af44f84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Ra25fc7bc48ef469f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rd2454d38fe9e47bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Ra6899c543f454946"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R1cf4369c0cff4e12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R3c77084ea0504b36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rc3f5f3be0c9f47ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rad8674d9c20546d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R8f38def6a3784dcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R7859c7bf4b5c4235"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R35a83af6c8e24263"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R0dfe374008514348"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Re1796c37d4ee4800"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Re4d6b04366904201"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R69f2f5dcccaf4783"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R1d17197fc1604052"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R82dc3298a7064a5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rbc4f18bb15dd4ca8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R146a3a2613f74a32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R19b299b7b21b4664"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rf810f65fde4d4bfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rc5ba2b4aa5d74747"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Re7abfef49d5c44bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rfa5352d9e8254d6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Re8b5bc121d1f45a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R890d74eac81d437e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rfe1ad63f5f4842ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R8ddae4cee8684833"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R07f7ab75c7b34a8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rea2b3216160a43ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Reca0ae39c2d24609"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R900f53d64ca7494f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R7eea3e6788814a31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R0346dfff3d794f45"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4367,7 +4367,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recb18b5570394865"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c6889bb5ee94aaa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5090,7 +5090,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94c28d59861c41d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbae895046c242b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5459,7 +5459,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f4ec0bd4dc04e64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bd2e8425c0d49f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5781,7 +5781,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raad78bc467e44bca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56c183664e8a4feb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6097,7 +6097,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1837d2b1ea524e9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R081a601829d84447"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6413,7 +6413,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R999bfac5c478450e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8f2d2e12190478c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6835,7 +6835,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc24ecb30885b48c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4c186f2566a4e9d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7159,7 +7159,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d759df862204570"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfbf3d3967ee4689"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7899,7 +7899,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fcbd82954844c81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3a567d58d284777"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8282,7 +8282,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5fc9e0628064f3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2021126768fa415b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8614,7 +8614,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bb16815d2734431"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fedf7c1a4494b4f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9187,7 +9187,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d7f00158f3440c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81ad8c7f2361413f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9503,7 +9503,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R308d60f745e241d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e4ef98cb88b4245"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10369,7 +10369,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a179570760f43f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3da2b38e65ca4cb6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10685,7 +10685,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c8d56e0c107434f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93a45d18c380461f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10999,7 +10999,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4597be362bd4cc9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcad056ef081a42ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11444,7 +11444,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra059169d33e04460"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ee0df4a5aaf4bc0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11879,7 +11879,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf461c0a8b9ad438e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9918e5fc86941bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12191,7 +12191,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59c775af8cf5462f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdfce6abbe7043d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13672,7 +13672,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb02885a62e0f4f8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58df317808c447b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13996,7 +13996,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6075db1c7c3646f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c586fed70604c9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14367,7 +14367,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36ca155bacc147f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd323312d6514f6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15115,7 +15115,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3cd3d7cb8714326"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6f6540470db4c97"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15431,7 +15431,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02d3736283fc47d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90752e12d3454cc9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15814,7 +15814,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree75f5a7ceaa436d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R798723bd96c94fb9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16173,7 +16173,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra24e92cea1604394"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f06601ed84b4a0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>